--- a/Datos escalados.xlsx
+++ b/Datos escalados.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Soporte\Documents\Escalados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB143BD4-C9CC-4DF2-A539-06D46F24EDCA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{CB143BD4-C9CC-4DF2-A539-06D46F24EDCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D63946A5-8FEA-4422-BBDD-461301D29302}"/>
   <bookViews>
     <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{9DC6A341-1742-49C4-824A-1E0B74086716}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,7 +23,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,17 +36,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="59">
   <si>
     <t>Ticket</t>
   </si>
   <si>
+    <t>Problema</t>
+  </si>
+  <si>
     <t>Usuario</t>
   </si>
   <si>
-    <t>Problema</t>
-  </si>
-  <si>
     <t>Motivo</t>
   </si>
   <si>
@@ -66,12 +71,12 @@
     <t>CUERVO AJA, YANKO</t>
   </si>
   <si>
+    <t>SMART.224415</t>
+  </si>
+  <si>
     <t>PROGRAMADO-Donacion de equipo obsoleto</t>
   </si>
   <si>
-    <t>SMART.224415</t>
-  </si>
-  <si>
     <t>SMART.224548</t>
   </si>
   <si>
@@ -111,12 +116,18 @@
     <t>Garcia Torres, Marina</t>
   </si>
   <si>
+    <t>Soporte</t>
+  </si>
+  <si>
     <t>SMART.224951</t>
   </si>
   <si>
     <t>ASAP - Santander</t>
   </si>
   <si>
+    <t>ITK</t>
+  </si>
+  <si>
     <t>SMART.225047</t>
   </si>
   <si>
@@ -159,6 +170,9 @@
     <t>PEREZ MORA, EMMANUEL DE JESÚS</t>
   </si>
   <si>
+    <t>SD</t>
+  </si>
+  <si>
     <t>SMART.225193</t>
   </si>
   <si>
@@ -181,6 +195,9 @@
   </si>
   <si>
     <t>Ramiro López, Alvaro</t>
+  </si>
+  <si>
+    <t>Compras</t>
   </si>
   <si>
     <t>SMART.225200</t>
@@ -202,7 +219,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,7 +269,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -549,23 +566,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{365DC760-7A34-4A22-868A-8F7A37600399}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="77.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="77.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -574,7 +591,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -588,7 +605,7 @@
         <v>45868</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -602,12 +619,12 @@
         <v>45868</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -616,7 +633,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -630,7 +647,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -644,7 +661,7 @@
         <v>46002</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -658,7 +675,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -672,7 +689,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -682,30 +699,36 @@
       <c r="C9" t="s">
         <v>25</v>
       </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
       <c r="E9" s="1">
         <v>46065</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
       </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
       <c r="E10" s="1">
         <v>46084</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
         <v>7</v>
@@ -714,124 +737,148 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
       </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
       <c r="E12" s="1">
         <v>46086</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
       </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
       <c r="E13" s="1">
         <v>46093</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
         <v>7</v>
       </c>
+      <c r="D14" t="s">
+        <v>2</v>
+      </c>
       <c r="E14" s="1">
         <v>46099</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2</v>
       </c>
       <c r="E15" s="1">
         <v>46104</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="D16" t="s">
+        <v>44</v>
       </c>
       <c r="E16" s="1">
         <v>46108</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
         <v>25</v>
       </c>
+      <c r="D17" t="s">
+        <v>44</v>
+      </c>
       <c r="E17" s="1">
         <v>46108</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" t="s">
         <v>44</v>
-      </c>
-      <c r="B18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" t="s">
-        <v>46</v>
       </c>
       <c r="E18" s="1">
         <v>46108</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>53</v>
       </c>
       <c r="E19" s="1">
         <v>46111</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
         <v>7</v>
@@ -840,15 +887,18 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>29</v>
       </c>
       <c r="E21" s="1">
         <v>46113</v>

--- a/Datos escalados.xlsx
+++ b/Datos escalados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Soporte\Documents\Escalados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{CB143BD4-C9CC-4DF2-A539-06D46F24EDCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D63946A5-8FEA-4422-BBDD-461301D29302}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{CB143BD4-C9CC-4DF2-A539-06D46F24EDCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D2099DB-0AF5-4ABB-AE60-6EE5956B2710}"/>
   <bookViews>
     <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{9DC6A341-1742-49C4-824A-1E0B74086716}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="61">
   <si>
     <t>Ticket</t>
   </si>
@@ -62,6 +62,9 @@
     <t>Arrazola Hernández, Israel (Mr.)</t>
   </si>
   <si>
+    <t>ITM</t>
+  </si>
+  <si>
     <t>SMART.224136</t>
   </si>
   <si>
@@ -77,6 +80,9 @@
     <t>PROGRAMADO-Donacion de equipo obsoleto</t>
   </si>
   <si>
+    <t>IAH</t>
+  </si>
+  <si>
     <t>SMART.224548</t>
   </si>
   <si>
@@ -86,6 +92,9 @@
     <t>GARCIA SANCHEZ, ULISES</t>
   </si>
   <si>
+    <t>SD</t>
+  </si>
+  <si>
     <t>SMART.224666</t>
   </si>
   <si>
@@ -98,6 +107,9 @@
     <t>PROGRAMADO -Quitar SWEET32 ASAP</t>
   </si>
   <si>
+    <t>ITK</t>
+  </si>
+  <si>
     <t>SMART.224926</t>
   </si>
   <si>
@@ -125,9 +137,6 @@
     <t>ASAP - Santander</t>
   </si>
   <si>
-    <t>ITK</t>
-  </si>
-  <si>
     <t>SMART.225047</t>
   </si>
   <si>
@@ -168,9 +177,6 @@
   </si>
   <si>
     <t>PEREZ MORA, EMMANUEL DE JESÚS</t>
-  </si>
-  <si>
-    <t>SD</t>
   </si>
   <si>
     <t>SMART.225193</t>
@@ -219,8 +225,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -248,9 +262,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -565,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{365DC760-7A34-4A22-868A-8F7A37600399}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
@@ -591,7 +606,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" ht="15">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -601,19 +616,25 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E2" s="1">
         <v>45868</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
       </c>
       <c r="E3" s="1">
         <v>45868</v>
@@ -621,27 +642,33 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
       <c r="E4" s="1">
         <v>45945</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
       </c>
       <c r="E5" s="1">
         <v>45979</v>
@@ -649,41 +676,50 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
       </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
       <c r="E6" s="1">
         <v>46002</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
       <c r="E7" s="1">
         <v>46050</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
       </c>
       <c r="E8" s="1">
         <v>46064</v>
@@ -691,16 +727,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1">
         <v>46065</v>
@@ -708,16 +744,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E10" s="1">
         <v>46084</v>
@@ -725,30 +761,33 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
         <v>7</v>
       </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
       <c r="E11" s="1">
         <v>46086</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E12" s="1">
         <v>46086</v>
@@ -756,16 +795,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E13" s="1">
         <v>46093</v>
@@ -773,10 +812,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
         <v>7</v>
@@ -790,13 +829,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
         <v>2</v>
@@ -807,16 +846,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E16" s="1">
         <v>46108</v>
@@ -824,16 +863,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E17" s="1">
         <v>46108</v>
@@ -841,16 +880,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E18" s="1">
         <v>46108</v>
@@ -858,16 +897,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E19" s="1">
         <v>46111</v>
@@ -875,34 +914,40 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
         <v>7</v>
       </c>
+      <c r="D20" t="s">
+        <v>8</v>
+      </c>
       <c r="E20" s="1">
         <v>46113</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E21" s="1">
         <v>46113</v>
       </c>
+    </row>
+    <row r="23" spans="1:5" ht="15">
+      <c r="D23" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datos escalados.xlsx
+++ b/Datos escalados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danna\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078BAD87-A817-44BB-A0E0-3EB81F36E47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00518E41-D49E-4BA8-BE14-FFC957AB25CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{9DC6A341-1742-49C4-824A-1E0B74086716}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
     <t>Ticket</t>
   </si>
@@ -114,6 +114,12 @@
   </si>
   <si>
     <t>HERNANDEZ SANCHEZ, MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>SMART.225302</t>
+  </si>
+  <si>
+    <t>BORRADO DE-CONFIGURACION DE SCANER</t>
   </si>
 </sst>
 </file>
@@ -149,10 +155,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{365DC760-7A34-4A22-868A-8F7A37600399}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
@@ -588,11 +593,28 @@
       <c r="C7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="1">
         <v>46127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1">
+        <v>46128</v>
       </c>
     </row>
   </sheetData>

--- a/Datos escalados.xlsx
+++ b/Datos escalados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danna\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00518E41-D49E-4BA8-BE14-FFC957AB25CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F78C4FE-DC45-4822-A98F-60996FCB7779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{9DC6A341-1742-49C4-824A-1E0B74086716}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{9DC6A341-1742-49C4-824A-1E0B74086716}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>Ticket</t>
   </si>
@@ -116,10 +116,13 @@
     <t>HERNANDEZ SANCHEZ, MARCO ANTONIO</t>
   </si>
   <si>
-    <t>SMART.225302</t>
-  </si>
-  <si>
-    <t>BORRADO DE-CONFIGURACION DE SCANER</t>
+    <t>SMART.225307</t>
+  </si>
+  <si>
+    <t>clave de yubikey</t>
+  </si>
+  <si>
+    <t>Vázquez Caballero, Ivonne</t>
   </si>
 </sst>
 </file>
@@ -608,13 +611,13 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E8" s="1">
-        <v>46128</v>
+        <v>46129</v>
       </c>
     </row>
   </sheetData>
